--- a/Decks/Arcades.xlsx
+++ b/Decks/Arcades.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB58474-182C-4558-B9C0-042FC6E4B4F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA76FD7D-7B9C-4F98-A27E-257D059E86D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B112A12-27E8-4BD4-BE1B-FA95246C7AB2}"/>
   </bookViews>
@@ -338,9 +338,6 @@
     <t>Bedrock Tortoise</t>
   </si>
   <si>
-    <t>Amuleto Simic</t>
-  </si>
-  <si>
     <t>Swiftfoot Boots</t>
   </si>
   <si>
@@ -354,6 +351,9 @@
   </si>
   <si>
     <t>Drift of Phantasms</t>
+  </si>
+  <si>
+    <t>Guardian of Faith</t>
   </si>
 </sst>
 </file>
@@ -1456,10 +1456,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2221,10 +2221,10 @@
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -2236,10 +2236,10 @@
         <v>0</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -2266,10 +2266,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -2281,10 +2281,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Arcades.xlsx
+++ b/Decks/Arcades.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA76FD7D-7B9C-4F98-A27E-257D059E86D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542CEE26-6425-4135-A96E-DE404BF52407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B112A12-27E8-4BD4-BE1B-FA95246C7AB2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="107">
   <si>
     <t>Função</t>
   </si>
@@ -206,9 +206,6 @@
     <t>Rampart Architect</t>
   </si>
   <si>
-    <t>Soulsworn Jury</t>
-  </si>
-  <si>
     <t>Wall of Blossoms</t>
   </si>
   <si>
@@ -275,9 +272,6 @@
     <t>True Conviction</t>
   </si>
   <si>
-    <t>Stoneskin</t>
-  </si>
-  <si>
     <t>Concerted Effort</t>
   </si>
   <si>
@@ -353,7 +347,16 @@
     <t>Drift of Phantasms</t>
   </si>
   <si>
-    <t>Guardian of Faith</t>
+    <t>Simic Charm</t>
+  </si>
+  <si>
+    <t>Captain America's Shield</t>
+  </si>
+  <si>
+    <t>Basilica Guards</t>
+  </si>
+  <si>
+    <t>Baxter Building</t>
   </si>
 </sst>
 </file>
@@ -1126,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1456,10 +1459,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1651,10 +1654,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -1666,10 +1669,10 @@
         <v>0</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -1681,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -1696,10 +1699,10 @@
         <v>0</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -1711,580 +1714,580 @@
         <v>0</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>60</v>
+      </c>
+      <c r="B64" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C64" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B64" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>62</v>
-      </c>
       <c r="D64" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" ref="B68:B101" si="1">C68&lt;&gt;D68</f>
         <v>0</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>70</v>
+      </c>
+      <c r="B73" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C73" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B73" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>72</v>
-      </c>
       <c r="D73" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>75</v>
+      </c>
+      <c r="B77" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C77" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B77" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="D77" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>82</v>
+      </c>
+      <c r="B85" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C85" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B85" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="D85" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>88</v>
+      </c>
+      <c r="B90" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C90" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B90" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>92</v>
-      </c>
       <c r="D90" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>95</v>
+      </c>
+      <c r="B96" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C96" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B96" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>99</v>
-      </c>
       <c r="D96" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
